--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7677,6 +7677,48 @@
         <v>395.52</v>
       </c>
       <c r="E345" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>322.58</v>
+      </c>
+      <c r="C346" t="n">
+        <v>323</v>
+      </c>
+      <c r="D346" t="n">
+        <v>396.72</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>318.67</v>
+      </c>
+      <c r="C347" t="n">
+        <v>318.39</v>
+      </c>
+      <c r="D347" t="n">
+        <v>396.33</v>
+      </c>
+      <c r="E347" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -7693,7 +7735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B387"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11566,6 +11608,26 @@
       </c>
       <c r="B387" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -11734,28 +11796,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04192409319418219</v>
+        <v>-0.06345366867636107</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006361109971547707</v>
+        <v>0.001457632361428041</v>
       </c>
       <c r="M2" t="n">
-        <v>9.640150895790031</v>
+        <v>9.671768442215701</v>
       </c>
       <c r="N2" t="n">
-        <v>151.5689467196876</v>
+        <v>152.5863447289024</v>
       </c>
       <c r="O2" t="n">
-        <v>12.31133407554549</v>
+        <v>12.35258453639976</v>
       </c>
       <c r="P2" t="n">
-        <v>339.9193975271039</v>
+        <v>340.1486039179458</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11812,28 +11874,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02213974099388778</v>
+        <v>0.000257210902173295</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001996606755346741</v>
+        <v>2.692780864954614e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>9.158575746539123</v>
+        <v>9.203810591524533</v>
       </c>
       <c r="N3" t="n">
-        <v>134.7280251089585</v>
+        <v>135.9131312612023</v>
       </c>
       <c r="O3" t="n">
-        <v>11.6072402020876</v>
+        <v>11.65817872830925</v>
       </c>
       <c r="P3" t="n">
-        <v>338.566185023462</v>
+        <v>338.7991507718745</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11890,28 +11952,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3846627912761224</v>
+        <v>0.3821374738422343</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1292565910999922</v>
+        <v>0.129251603944765</v>
       </c>
       <c r="M4" t="n">
-        <v>5.720329714961717</v>
+        <v>5.697529611053008</v>
       </c>
       <c r="N4" t="n">
-        <v>54.71293134044836</v>
+        <v>54.42265188320487</v>
       </c>
       <c r="O4" t="n">
-        <v>7.396819001465992</v>
+        <v>7.377170994575419</v>
       </c>
       <c r="P4" t="n">
-        <v>388.322474550718</v>
+        <v>388.3493592157918</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -11949,7 +12011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21267,6 +21329,60 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.83922233866977,174.5793457693898</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.8399659207519,174.5794788428344</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.8405049177713,174.58050887409172</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.83922754520226,174.57930295993103</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.839974747007304,174.57942897336792</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.84050588922201,174.58050472477794</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E347"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7721,6 +7721,69 @@
       <c r="E347" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>319.65</v>
+      </c>
+      <c r="C348" t="n">
+        <v>318.84</v>
+      </c>
+      <c r="D348" t="n">
+        <v>396.48</v>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>322.49</v>
+      </c>
+      <c r="C349" t="n">
+        <v>320.14</v>
+      </c>
+      <c r="D349" t="n">
+        <v>397.22</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>324.34</v>
+      </c>
+      <c r="C350" t="n">
+        <v>320.14</v>
+      </c>
+      <c r="D350" t="n">
+        <v>397.22</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11628,6 +11691,36 @@
       </c>
       <c r="B389" t="n">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>
@@ -11796,28 +11889,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06345366867636107</v>
+        <v>-0.09177005654486006</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001457632361428041</v>
+        <v>0.003060251933834746</v>
       </c>
       <c r="M2" t="n">
-        <v>9.671768442215701</v>
+        <v>9.703191090860717</v>
       </c>
       <c r="N2" t="n">
-        <v>152.5863447289024</v>
+        <v>153.5206156650744</v>
       </c>
       <c r="O2" t="n">
-        <v>12.35258453639976</v>
+        <v>12.39034364596376</v>
       </c>
       <c r="P2" t="n">
-        <v>340.1486039179458</v>
+        <v>340.4510262764259</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11874,28 +11967,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000257210902173295</v>
+        <v>-0.03297238622331967</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L3" t="n">
-        <v>2.692780864954614e-08</v>
+        <v>0.0004412932986249674</v>
       </c>
       <c r="M3" t="n">
-        <v>9.203810591524533</v>
+        <v>9.274570361877752</v>
       </c>
       <c r="N3" t="n">
-        <v>135.9131312612023</v>
+        <v>137.7953952424982</v>
       </c>
       <c r="O3" t="n">
-        <v>11.65817872830925</v>
+        <v>11.73862833735263</v>
       </c>
       <c r="P3" t="n">
-        <v>338.7991507718745</v>
+        <v>339.1540819931907</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -11952,28 +12045,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3821374738422343</v>
+        <v>0.379225873177174</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>0.129251603944765</v>
+        <v>0.1297392906370713</v>
       </c>
       <c r="M4" t="n">
-        <v>5.697529611053008</v>
+        <v>5.660190566514511</v>
       </c>
       <c r="N4" t="n">
-        <v>54.42265188320487</v>
+        <v>53.97923823672262</v>
       </c>
       <c r="O4" t="n">
-        <v>7.377170994575419</v>
+        <v>7.347056433478826</v>
       </c>
       <c r="P4" t="n">
-        <v>388.3493592157918</v>
+        <v>388.3804541431976</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12011,7 +12104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E347"/>
+  <dimension ref="A1:E350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21383,6 +21476,87 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.83922624024157,174.57931368966808</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.83997388544314,174.5794338413207</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.84050551558713,174.58050632066787</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>-35.8392224585134,174.57934478400588</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>-35.839971396478916,174.57944790429477</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>-35.84050367232146,174.58051419372464</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>-35.83921999505942,174.57936503911856</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>-35.839971396478916,174.57944790429477</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>-35.84050367232146,174.58051419372464</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0103/nzd0103.xlsx
+++ b/data/nzd0103/nzd0103.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7784,6 +7784,27 @@
       <c r="E350" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="C351" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="D351" t="n">
+        <v>397.98</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -7798,7 +7819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B392"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11721,6 +11742,16 @@
       </c>
       <c r="B392" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -11889,28 +11920,28 @@
         <v>0.055</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09177005654486006</v>
+        <v>-0.09978816369554107</v>
       </c>
       <c r="J2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003060251933834746</v>
+        <v>0.003627593602886225</v>
       </c>
       <c r="M2" t="n">
-        <v>9.703191090860717</v>
+        <v>9.707543226715448</v>
       </c>
       <c r="N2" t="n">
-        <v>153.5206156650744</v>
+        <v>153.6235392501173</v>
       </c>
       <c r="O2" t="n">
-        <v>12.39034364596376</v>
+        <v>12.39449632902109</v>
       </c>
       <c r="P2" t="n">
-        <v>340.4510262764259</v>
+        <v>340.5370257366203</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -11967,28 +11998,28 @@
         <v>0.0756</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03297238622331967</v>
+        <v>-0.04352939697338043</v>
       </c>
       <c r="J3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004412932986249674</v>
+        <v>0.0007687384184215107</v>
       </c>
       <c r="M3" t="n">
-        <v>9.274570361877752</v>
+        <v>9.296130353388355</v>
       </c>
       <c r="N3" t="n">
-        <v>137.7953952424982</v>
+        <v>138.3405088893786</v>
       </c>
       <c r="O3" t="n">
-        <v>11.73862833735263</v>
+        <v>11.76182421605503</v>
       </c>
       <c r="P3" t="n">
-        <v>339.1540819931907</v>
+        <v>339.2673128603655</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -12045,28 +12076,28 @@
         <v>0.0704</v>
       </c>
       <c r="I4" t="n">
-        <v>0.379225873177174</v>
+        <v>0.3788420111273322</v>
       </c>
       <c r="J4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1297392906370713</v>
+        <v>0.13025925098865</v>
       </c>
       <c r="M4" t="n">
-        <v>5.660190566514511</v>
+        <v>5.64553094798764</v>
       </c>
       <c r="N4" t="n">
-        <v>53.97923823672262</v>
+        <v>53.82625306056091</v>
       </c>
       <c r="O4" t="n">
-        <v>7.347056433478826</v>
+        <v>7.336637721774253</v>
       </c>
       <c r="P4" t="n">
-        <v>388.3804541431976</v>
+        <v>388.3845713155494</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12104,7 +12135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E350"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21557,6 +21588,33 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:11:40+00:00</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>-35.83922026137893,174.5793628493767</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>-35.839971568791874,174.57944693070428</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>-35.840501779237286,174.5805222795663</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
